--- a/jpcore-r4b/feature/merge-v1.2.0/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4b/feature/merge-v1.2.0/StructureDefinition-jp-observation-labresult.xlsx
@@ -1516,7 +1516,7 @@
   <si>
     <t>【JP Core仕様】拡張可コード表「ObservationInterpretationCodes」を使用する。  
 コード表が大きいため、下記参照。  
-https://www.hl7.org/fhir/R4/valueset-observation-interpretation.html</t>
+https://www.hl7.org/fhir/R4B/valueset-observation-interpretation.html</t>
   </si>
   <si>
     <t>特に数値結果については、結果の重要性を完全に理解するために解釈を必要とする場合がある。</t>
